--- a/data/trans_orig/P41C_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P41C_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han tenido o tienen dificultades para tener un embarazo en 2023</t>
+          <t>Población según si han tenido o tienen dificultades para tener un embarazo en 2023 (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100176</t>
+          <t>100541</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110350</t>
+          <t>110131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100468</t>
+          <t>100403</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110072</t>
+          <t>109960</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>204179</t>
+          <t>205959</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>218269</t>
+          <t>218338</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,47 +1006,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>8062</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>4136</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>14116</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>8062</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>4391</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>14669</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74535</t>
+          <t>73742</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82647</t>
+          <t>82609</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93416</t>
+          <t>92698</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103032</t>
+          <t>103145</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>171861</t>
+          <t>171967</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184564</t>
+          <t>184336</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>8990</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>315970</t>
+          <t>316719</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25713</t>
+          <t>25880</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>350089</t>
+          <t>350466</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26739</t>
+          <t>27535</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>22357</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>188311</t>
+          <t>190184</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201580</t>
+          <t>201150</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>181005</t>
+          <t>180643</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>188686</t>
+          <t>188473</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>373543</t>
+          <t>373676</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>387969</t>
+          <t>388305</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>969</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>10858</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>605</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>88370</t>
+          <t>88230</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>140678</t>
+          <t>141202</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>148904</t>
+          <t>149019</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>232919</t>
+          <t>233172</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>243299</t>
+          <t>243061</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7913</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>80524</t>
+          <t>79956</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>98618</t>
+          <t>98869</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>817967</t>
+          <t>819915</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>851862</t>
+          <t>852400</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>637698</t>
+          <t>637532</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>655767</t>
+          <t>655259</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1467090</t>
+          <t>1465724</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1506886</t>
+          <t>1505883</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>9964</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>22243</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>9269</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>22256</t>
+          <t>22334</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>14863</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>38701</t>
+          <t>38125</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>11299</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>21393</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>29545</t>
+          <t>30544</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41C_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P41C_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>106676</t>
+          <t>115668</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100541</t>
+          <t>108519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110131</t>
+          <t>118813</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>106227</t>
+          <t>114383</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100403</t>
+          <t>108486</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>109960</t>
+          <t>118426</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>212903</t>
+          <t>230051</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205959</t>
+          <t>222001</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>218338</t>
+          <t>235466</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9392</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14116</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>979</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>773</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>111761</t>
+          <t>120792</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>111761</t>
+          <t>120792</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111761</t>
+          <t>120792</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>113767</t>
+          <t>122133</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>113767</t>
+          <t>122133</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>113767</t>
+          <t>122133</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>225528</t>
+          <t>242925</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>225528</t>
+          <t>242925</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>225528</t>
+          <t>242925</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>80254</t>
+          <t>86637</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73742</t>
+          <t>80797</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82609</t>
+          <t>89075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>98897</t>
+          <t>108045</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92698</t>
+          <t>101622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103145</t>
+          <t>112589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>179151</t>
+          <t>194682</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>171967</t>
+          <t>185637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184336</t>
+          <t>200274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>709</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>9449</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>14277</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83670</t>
+          <t>90183</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83670</t>
+          <t>90183</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83670</t>
+          <t>90183</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>108053</t>
+          <t>117660</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>108053</t>
+          <t>117660</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>108053</t>
+          <t>117660</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>191723</t>
+          <t>207843</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>191723</t>
+          <t>207843</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>191723</t>
+          <t>207843</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,69 +2089,69 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>341085</t>
+          <t>104688</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>316719</t>
+          <t>90151</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>346882</t>
+          <t>109819</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>33897</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>30221</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>34638</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>87,25%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>29303</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>25880</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>29985</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>86,31%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>137</t>
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>370388</t>
+          <t>138586</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>350466</t>
+          <t>123298</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>376867</t>
+          <t>143835</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>741</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>741</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27535</t>
+          <t>19257</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>20222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>346882</t>
+          <t>111050</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>346882</t>
+          <t>111050</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>346882</t>
+          <t>111050</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29985</t>
+          <t>34638</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29985</t>
+          <t>34638</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29985</t>
+          <t>34638</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>376867</t>
+          <t>145688</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>376867</t>
+          <t>145688</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>376867</t>
+          <t>145688</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>196682</t>
+          <t>216408</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>190184</t>
+          <t>208254</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201150</t>
+          <t>221888</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>185763</t>
+          <t>207564</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>180643</t>
+          <t>202677</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>188473</t>
+          <t>210066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>382445</t>
+          <t>423971</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>373676</t>
+          <t>414160</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>388305</t>
+          <t>430357</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>870</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2296</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,67 +3258,67 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>4464</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>9884</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>4403</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1606</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>9860</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>205347</t>
+          <t>226199</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>205347</t>
+          <t>226199</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>205347</t>
+          <t>226199</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>190133</t>
+          <t>212021</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>190133</t>
+          <t>212021</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>190133</t>
+          <t>212021</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>395480</t>
+          <t>438219</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>395480</t>
+          <t>438219</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>395480</t>
+          <t>438219</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,27 +3453,27 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>93384</t>
+          <t>107634</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>88230</t>
+          <t>99148</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>94837</t>
+          <t>109091</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>146050</t>
+          <t>163919</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>141202</t>
+          <t>157873</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>149019</t>
+          <t>167423</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>239435</t>
+          <t>271553</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>233172</t>
+          <t>264313</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>243061</t>
+          <t>275436</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>728</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>728</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>94837</t>
+          <t>109091</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>94837</t>
+          <t>109091</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>94837</t>
+          <t>109091</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>151925</t>
+          <t>171250</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>151925</t>
+          <t>171250</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>151925</t>
+          <t>171250</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>246763</t>
+          <t>280341</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>246763</t>
+          <t>280341</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>246763</t>
+          <t>280341</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4170,27 +4170,27 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>81842</t>
+          <t>91798</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>79956</t>
+          <t>89990</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>82195</t>
+          <t>92143</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4205,27 +4205,27 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>100334</t>
+          <t>111264</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>98869</t>
+          <t>109708</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>100687</t>
+          <t>111609</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>345</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>345</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>82195</t>
+          <t>92143</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>82195</t>
+          <t>92143</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>82195</t>
+          <t>92143</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>100687</t>
+          <t>111609</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>100687</t>
+          <t>111609</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>100687</t>
+          <t>111609</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>836575</t>
+          <t>650500</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>819915</t>
+          <t>634900</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>852400</t>
+          <t>661255</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>648083</t>
+          <t>719606</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>637532</t>
+          <t>708172</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>655259</t>
+          <t>727910</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1484657</t>
+          <t>1370107</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1465724</t>
+          <t>1353014</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1505883</t>
+          <t>1383716</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,22 +4965,22 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>8250</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>11505</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>12127</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>22243</t>
+          <t>21144</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>9794</t>
+          <t>10573</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>22334</t>
+          <t>24692</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>28623</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>20110</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>38125</t>
+          <t>39881</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>13233</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>21249</t>
+          <t>22325</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8594</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>14822</t>
+          <t>16636</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>9745</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>30544</t>
+          <t>31566</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>860991</t>
+          <t>676780</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>860991</t>
+          <t>676780</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>860991</t>
+          <t>676780</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>676059</t>
+          <t>749845</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>676059</t>
+          <t>749845</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>676059</t>
+          <t>749845</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1537049</t>
+          <t>1426626</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1537049</t>
+          <t>1426626</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1537049</t>
+          <t>1426626</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
